--- a/Data Analysis/1_Data/Aggregates/Results_Spring2024_WSA_all.xlsx
+++ b/Data Analysis/1_Data/Aggregates/Results_Spring2024_WSA_all.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mm68tulo\Desktop\Jena Chapter\Data Analysis\1_Data\Aggregates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D074A178-7A72-4CC0-A7CD-872E10A7E00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99E28134-19A1-4012-9787-1FB29FED4114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="110">
   <si>
     <t>Number</t>
   </si>
@@ -386,6 +386,9 @@
   </si>
   <si>
     <t>agg_overall</t>
+  </si>
+  <si>
+    <t>WSA</t>
   </si>
 </sst>
 </file>
@@ -839,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="M1" s="1" t="s">
         <v>11</v>
